--- a/config/excel/CfgRooms.xlsx
+++ b/config/excel/CfgRooms.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRooms" sheetId="1" r:id="R8bd64f3394314f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRooms" sheetId="1" r:id="R95de97d34b1d43ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,29 +13,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="1">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="2">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF17365D"/>
-      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -50,10 +39,8 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -257,44 +244,47 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="2" t="str">
+      <x:c r="A1" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="str">
+      <x:c r="B1" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="str">
+      <x:c r="C1" t="str">
         <x:v>Kind</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="str">
+      <x:c r="D1" t="str">
         <x:v>MapID</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="str">
+      <x:c r="E1" t="str">
         <x:v>EncounterID</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="str">
+      <x:c r="F1" t="str">
         <x:v>BossID</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="str">
+      <x:c r="G1" t="str">
         <x:v>ChestPoolID</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="str">
+      <x:c r="H1" t="str">
         <x:v>NpcPoolID</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="str">
+      <x:c r="I1" t="str">
         <x:v>EnemyLevelOffset</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="str">
+      <x:c r="J1" t="str">
         <x:v>InteractionRadius</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="str">
+      <x:c r="K1" t="str">
         <x:v>ReachabilityGridSpacing</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="str">
+      <x:c r="L1" t="str">
         <x:v>ReachabilityMaxCells</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="str">
+      <x:c r="M1" t="str">
         <x:v>MaxSpawnSlots</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>ChestCount</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -335,6 +325,9 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="M2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
         <x:v>int</x:v>
       </x:c>
     </x:row>
@@ -374,6 +367,9 @@
       <x:c r="M3" t="n">
         <x:v>64</x:v>
       </x:c>
+      <x:c r="N3" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="n">
@@ -413,6 +409,9 @@
       <x:c r="M4" t="n">
         <x:v>64</x:v>
       </x:c>
+      <x:c r="N4" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="n">
@@ -450,6 +449,9 @@
       <x:c r="M5" t="n">
         <x:v>64</x:v>
       </x:c>
+      <x:c r="N5" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="n">
@@ -488,6 +490,9 @@
       </x:c>
       <x:c r="M6" t="n">
         <x:v>64</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -526,6 +531,9 @@
       <x:c r="M7" t="n">
         <x:v>64</x:v>
       </x:c>
+      <x:c r="N7" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="n">
@@ -563,6 +571,9 @@
       <x:c r="M8" t="n">
         <x:v>64</x:v>
       </x:c>
+      <x:c r="N8" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
